--- a/results/0916-all/琼雷及南海诸岛农林区/tech_selected_summary.xlsx
+++ b/results/0916-all/琼雷及南海诸岛农林区/tech_selected_summary.xlsx
@@ -106,196 +106,196 @@
     <t>洋浦区</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -319,7 +319,7 @@
     <t>4R(Right place)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 15735422.58</t>
+    <t>15735422.58</t>
   </si>
   <si>
     <t>Low protein diet_Pig</t>
@@ -343,7 +343,7 @@
     <t>cover crop (mix)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 32298042.08</t>
+    <t>32298042.08</t>
   </si>
   <si>
     <t>Yucca extract_sheep &amp; goat</t>
@@ -475,7 +475,7 @@
     <t>irrigation (AWD irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 328927486.16</t>
+    <t>328927486.16</t>
   </si>
   <si>
     <t>Increasing byproduct_pig</t>
@@ -514,13 +514,13 @@
     <t>nitrification inhibitor_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 459217402.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 332972075.39</t>
+    <t>459217402.20</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>332972075.39</t>
   </si>
   <si>
     <t>Cover_sheep&amp;goat</t>
@@ -529,7 +529,7 @@
     <t>4R(Right place)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 102657856.75</t>
+    <t>102657856.75</t>
   </si>
   <si>
     <t>Yucca extract_Beef cattle</t>
@@ -541,13 +541,13 @@
     <t>Zeolite_Poultry</t>
   </si>
   <si>
-    <t>总经济成本: 281797642.33</t>
+    <t>281797642.33</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 258499592.46</t>
+    <t>258499592.46</t>
   </si>
   <si>
     <t>Probiotics_pig</t>
@@ -586,13 +586,13 @@
     <t>cover crop (non-leguminous)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 443133248.10</t>
-  </si>
-  <si>
-    <t>总经济成本: 240768473.59</t>
-  </si>
-  <si>
-    <t>总经济成本: 156065981.69</t>
+    <t>443133248.10</t>
+  </si>
+  <si>
+    <t>240768473.59</t>
+  </si>
+  <si>
+    <t>156065981.69</t>
   </si>
   <si>
     <t>nitrification inhibitor_beef cattle</t>
@@ -643,31 +643,31 @@
     <t>irrigation (water-saving irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 222516266.95</t>
+    <t>222516266.95</t>
   </si>
   <si>
     <t>Feedstock adjustment_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 74949731.75</t>
+    <t>74949731.75</t>
   </si>
   <si>
     <t>4R(Right type)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 119198408.75</t>
-  </si>
-  <si>
-    <t>总经济成本: 282481163.72</t>
+    <t>119198408.75</t>
+  </si>
+  <si>
+    <t>282481163.72</t>
   </si>
   <si>
     <t>Frequent removal_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 132836592.39</t>
-  </si>
-  <si>
-    <t>总经济成本: 3280011.24</t>
+    <t>132836592.39</t>
+  </si>
+  <si>
+    <t>3280011.24</t>
   </si>
   <si>
     <t>chemical amendments_dairy</t>
@@ -676,7 +676,7 @@
     <t>Chemical amendments_pig</t>
   </si>
   <si>
-    <t>总经济成本: 124818743.58</t>
+    <t>124818743.58</t>
   </si>
   <si>
     <t>Cover_dairy</t>
@@ -688,28 +688,28 @@
     <t>cover crop (mix)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 1052576662.76</t>
+    <t>1052576662.76</t>
   </si>
   <si>
     <t>Urease Inhibitor_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 63354959.18</t>
-  </si>
-  <si>
-    <t>总经济成本: 248144953.59</t>
-  </si>
-  <si>
-    <t>总经济成本: 359269478.28</t>
-  </si>
-  <si>
-    <t>总经济成本: 2951260.99</t>
+    <t>63354959.18</t>
+  </si>
+  <si>
+    <t>248144953.59</t>
+  </si>
+  <si>
+    <t>359269478.28</t>
+  </si>
+  <si>
+    <t>2951260.99</t>
   </si>
   <si>
     <t>Adsorbent_poultry</t>
   </si>
   <si>
-    <t>总经济成本: 95927470.98</t>
+    <t>95927470.98</t>
   </si>
   <si>
     <t>Yucca extract_Poultry</t>
@@ -742,7 +742,7 @@
     <t>tillage management (zero tillage)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 669873127.54</t>
+    <t>669873127.54</t>
   </si>
 </sst>
 </file>
